--- a/InputFiles/GC/TC02_GC_phs001905_Sex_Unknown_ExpStr-TargetedSeq_FileTyp-CRAM.xlsx
+++ b/InputFiles/GC/TC02_GC_phs001905_Sex_Unknown_ExpStr-TargetedSeq_FileTyp-CRAM.xlsx
@@ -506,13 +506,13 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+          <t>MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
 WHERE s.phs_accession = "phs001905"
   AND p.sex = "Unknown"
   AND toLower(f.file_type) = toLower("CRAM")
   AND f.experimental_strategy_and_data_subtypes CONTAINS "Targeted Sequencing"
-WITH DISTINCT p, s
-OPTIONAL MATCH (samp_all:sample)-[:of_participant]-&gt;(p)
+WITH DISTINCT p, s, f
+OPTIONAL MATCH (f)-[:from_sample]-&gt;(samp_all:sample)
 WITH p, s, samp_all
 ORDER BY samp_all.sample_id ASC
 WITH p, s, [x IN collect(samp_all.sample_id) WHERE x IS NOT NULL] AS sample_ids
@@ -529,34 +529,32 @@
   p.sex AS sex,
   samples
 ORDER BY p.participant_id ASC
-LIMIT 100
-</t>
+LIMIT 100</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+          <t>MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+MATCH (f)-[:from_sample]-&gt;(samp:sample)
 WHERE s.phs_accession = "phs001905"
   AND p.sex = "Unknown"
   AND toLower(f.file_type) = toLower("CRAM")
   AND f.experimental_strategy_and_data_subtypes CONTAINS "Targeted Sequencing"
-OPTIONAL MATCH (f)-[:from_sample]-&gt;(samp:sample)
 RETURN
   count(DISTINCT s) AS Studies,
   count(DISTINCT p) AS Participants,
   count(DISTINCT samp) AS Samples,
-  count(DISTINCT f) AS Files
-</t>
+  count(DISTINCT f) AS Files</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TC02_CDS_phs001905_gender_Unknown_ExpStr-TargetedSeq_FileTyp-CRAM_TSVData.xlsx</t>
+          <t>TC02_CDS_phs001905_Sex_Unknown_ExpStr-TargetedSeq_FileTyp-CRAM_TSVData.xlsx</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TC02_CDS_phs001905_gender_Unknown_ExpStr-TargetedSeq_FileTyp-CRAM_WebData.xlsx</t>
+          <t>TC02_CDS_phs001905_Sex_Unknown_ExpStr-TargetedSeq_FileTyp-CRAM_WebData.xlsx</t>
         </is>
       </c>
     </row>
@@ -568,7 +566,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (f:file)-[:from_sample]-&gt;(samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+          <t>MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+MATCH (f)-[:from_sample]-&gt;(samp:sample)
 WHERE s.phs_accession = "phs001905"
   AND p.sex = "Unknown"
   AND toLower(f.file_type) = toLower("CRAM")
@@ -580,8 +579,7 @@
   COALESCE(samp.sample_name, samp.sample_id) AS sample_name,
   COALESCE(samp.Organization_Name, "Not specified in data") AS organization_name
 ORDER BY samp.sample_id ASC
-LIMIT 100
-</t>
+LIMIT 100</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -594,22 +592,21 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+          <t>MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+MATCH (f)-[:from_sample]-&gt;(samp:sample)
 WHERE s.phs_accession = "phs001905"
   AND p.sex = "Unknown"
   AND toLower(f.file_type) = toLower("CRAM")
   AND f.experimental_strategy_and_data_subtypes CONTAINS "Targeted Sequencing"
-OPTIONAL MATCH (f)-[:from_sample]-&gt;(samp:sample)
 RETURN DISTINCT
   s.study_name AS study_name,
   s.phs_accession AS accession,
   f.file_name AS file_name,
   f.file_id AS file_id,
   f.file_type AS file_type,
-  COALESCE(samp.sample_id, "Not Applicable") AS sample_id
+  samp.sample_id AS sample_id
 ORDER BY f.file_name ASC
-LIMIT 100
-</t>
+LIMIT 100</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
